--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyVariables" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SignalLedger" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegimeHistory" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VariableRegistry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalystLog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataQuality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditAdditionLog" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerformanceStats" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MethodologyNotes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DailyVariables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SignalLedger" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RegimeHistory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VariableRegistry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CatalystLog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DataQuality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AuditAdditionLog" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PerformanceStats" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="README" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MethodologyNotes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DailyVariables'!$A$1:$BY$1</definedName>
@@ -1719,52 +1719,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>MetaIntegration-Phase2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Phase 2 data pipeline: V001/V004 A→B downgrade; V029-V035 registry rows added; SignalLedger +4 cols (overlay_gate_status, v027_regime_bucket, bab_sleeve_weight, dealergamma_sleeve_weight); scripts/compute_meta_additions.py created; preflight-meta-additions-1952pm scheduled task created (shadow mode Mon-Fri); meta-shadow-mode-review-2026-04-25 one-time review task created.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>meta-analysis-integration-plan-2026-04-18.md; deployment-memo-2026-04-18.md</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>VariableRegistry; SignalLedger</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>V001; V004; V029; V030; V031; V032; V033; V034; V035</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Executed on delegated judgment (2026-04-18 "Recommend and execute")</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Cowork session 2026-04-18</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Shadow mode Mon-Fri 2026-04-20..04-24. Review fires 2026-04-25 10:00 UTC+8. V030 MISSING until subscription confirmed; V031/V032 stub-only pending Phase 2b self-compute implementation.</t>
         </is>
@@ -12278,7 +12278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -13370,6 +13370,321 @@
       <c r="I24" s="13" t="inlineStr">
         <is>
           <t>trade-rec-2026-04-17.md v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V029 BAB (ETF proxy)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USMV/SPLV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RETRIEVED — ANTI-BAB spread -0.63% (USMV +3.04% - SPLV +3.67%)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V030 DealerGamma</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MISSING — subscription pending (SqueezeMetrics/SpotGamma)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V031 GP/A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MISSING — Phase 2 stub, Ken French GP CSV fetcher not implemented</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>V032 CEI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MISSING — Phase 2 stub, compute_cei.py not implemented</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V033 Faber SPY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RETRIEVED — Gate ON (close 710.14 vs 10m-SMA 669.57, +6.06%)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V034 Faber GSCI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GSG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RETRIEVED — Gate ON (close 30.35 vs 10m-SMA 25.21, +20.39%)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>V035 Faber BTC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RETRIEVED — Gate OFF (close 77126.88 vs 10m-SMA 91648.75, -15.94%)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SHADOW</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/A (shadow mode, not scored)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-04-20/meta-additions-staging-2026-04-20.md</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyVariables" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SignalLedger" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegimeHistory" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VariableRegistry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalystLog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataQuality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditAdditionLog" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerformanceStats" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MethodologyNotes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DailyVariables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SignalLedger" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RegimeHistory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VariableRegistry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CatalystLog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DataQuality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AuditAdditionLog" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PerformanceStats" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="README" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MethodologyNotes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DailyVariables'!$A$1:$BY$1</definedName>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:BY5"/>
+  <dimension ref="A1:BY6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -1584,6 +1584,145 @@
       <c r="BY5" s="13" t="inlineStr">
         <is>
           <t>market-brief-2026-04-17 v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>65.69499999999999</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>98.224</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>2.356</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="S6" s="13" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="T6" s="13" t="n">
+        <v>648.85</v>
+      </c>
+      <c r="U6" s="13" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="V6" s="13" t="n">
+        <v>152.33</v>
+      </c>
+      <c r="W6" s="13" t="n">
+        <v>201.68</v>
+      </c>
+      <c r="X6" s="13" t="n">
+        <v>400.62</v>
+      </c>
+      <c r="Y6" s="13" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="Z6" s="13" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="AA6" s="13" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="AB6" s="13" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="AC6" s="13" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="AD6" s="13" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AE6" s="13" t="n">
+        <v>455.07</v>
+      </c>
+      <c r="AF6" s="13" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AG6" s="13" t="n">
+        <v>146.39</v>
+      </c>
+      <c r="AH6" s="13" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="AU6" s="13" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="AV6" s="13" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="AW6" s="13" t="n">
+        <v>4830.7</v>
+      </c>
+      <c r="AX6" s="13" t="n">
+        <v>79.91500000000001</v>
+      </c>
+      <c r="AY6" s="13" t="n">
+        <v>6.036</v>
+      </c>
+      <c r="AZ6" s="13" t="n">
+        <v>2090.7</v>
+      </c>
+      <c r="BA6" s="13" t="n">
+        <v>1552</v>
+      </c>
+      <c r="BL6" s="13" t="n">
+        <v>1.1763</v>
+      </c>
+      <c r="BM6" s="13" t="n">
+        <v>158.898</v>
+      </c>
+      <c r="BN6" s="13" t="n">
+        <v>75370.60000000001</v>
+      </c>
+      <c r="BO6" s="13" t="n">
+        <v>2313.3</v>
+      </c>
+      <c r="BP6" s="13" t="n">
+        <v>1064.99</v>
+      </c>
+      <c r="BQ6" s="13" t="n">
+        <v>396267</v>
+      </c>
+      <c r="BX6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY6" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
         </is>
       </c>
     </row>
@@ -1719,52 +1858,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>MetaIntegration-Phase2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Phase 2 data pipeline: V001/V004 A→B downgrade; V029-V035 registry rows added; SignalLedger +4 cols (overlay_gate_status, v027_regime_bucket, bab_sleeve_weight, dealergamma_sleeve_weight); scripts/compute_meta_additions.py created; preflight-meta-additions-1952pm scheduled task created (shadow mode Mon-Fri); meta-shadow-mode-review-2026-04-25 one-time review task created.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>meta-analysis-integration-plan-2026-04-18.md; deployment-memo-2026-04-18.md</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>VariableRegistry; SignalLedger</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>V001; V004; V029; V030; V031; V032; V033; V034; V035</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Executed on delegated judgment (2026-04-18 "Recommend and execute")</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Cowork session 2026-04-18</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Shadow mode Mon-Fri 2026-04-20..04-24. Review fires 2026-04-25 10:00 UTC+8. V030 MISSING until subscription confirmed; V031/V032 stub-only pending Phase 2b self-compute implementation.</t>
         </is>
@@ -1781,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -2309,8 +2448,25 @@
       </c>
       <c r="W4" s="17" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>HIT_TARGET</t>
+        </is>
+      </c>
+      <c r="X4" s="13" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="Y4" s="26" t="n">
+        <v>46131</v>
+      </c>
+      <c r="Z4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="13" t="inlineStr">
+        <is>
+          <t>EXITED_PRE_CATALYST</t>
+        </is>
+      </c>
+      <c r="AD4" s="13" t="n">
+        <v>0.57</v>
       </c>
       <c r="AE4" s="17" t="inlineStr">
         <is>
@@ -2319,7 +2475,7 @@
       </c>
       <c r="AF4" s="17" t="inlineStr">
         <is>
-          <t>Residual +42.33% T=+1. Semi-correlated with EWY. TAKEN 2026-04-16 09:29 UTC+8. Market buy filled at $64.68 ($49.81 USDT). Above rec entry zone $60-$64; size reduced accordingly.</t>
+          <t>Closed 2026-04-19 21:31 UTC+8 before Apr-23 earnings. Memory.md entry $64.68 vs Binance fill $67.87 — entry-price discrepancy noted.</t>
         </is>
       </c>
       <c r="AG4" s="13" t="inlineStr">
@@ -4061,8 +4217,25 @@
       </c>
       <c r="W22" s="13" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>HIT_TARGET</t>
+        </is>
+      </c>
+      <c r="X22" s="13" t="n">
+        <v>4823.65</v>
+      </c>
+      <c r="Y22" s="26" t="n">
+        <v>46130</v>
+      </c>
+      <c r="Z22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="13" t="inlineStr">
+        <is>
+          <t>EXITED_PRE_CATALYST</t>
+        </is>
+      </c>
+      <c r="AD22" s="13" t="n">
+        <v>0.9</v>
       </c>
       <c r="AE22" s="13" t="inlineStr">
         <is>
@@ -4071,7 +4244,7 @@
       </c>
       <c r="AF22" s="13" t="inlineStr">
         <is>
-          <t>Iran ceasefire Apr-21 = C+1. Basis-momentum MISSING but Gold S from DXY/real yields. Checklist 6/6 PASS. Reaffirmed v3: basis-momentum confirmed (contango, no divergence cap). | EXECUTED 2026-04-16 22:28 UTC+8 at actual fill $4,780.69 (trailing buy triggered ≤$4,798.34, 0.1% callback); size $396.80 USDT ~0.0830 oz. Fill BELOW stated entry zone $4,800–$4,860 — trailing stop caught the dip, favorable. Entry_Price kept as signal-time $4,840. Reconciled 2026-04-17.</t>
+          <t>Closed 2026-04-18 17:12 UTC+8 before Apr-22 ceasefire binary. DXY + real-yield thesis intact at exit.</t>
         </is>
       </c>
       <c r="AG22" s="13" t="inlineStr">
@@ -4777,8 +4950,25 @@
       </c>
       <c r="W29" s="13" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>HIT_TARGET</t>
+        </is>
+      </c>
+      <c r="X29" s="13" t="n">
+        <v>643.02</v>
+      </c>
+      <c r="Y29" s="26" t="n">
+        <v>46131</v>
+      </c>
+      <c r="Z29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="13" t="inlineStr">
+        <is>
+          <t>EXITED_PRE_CATALYST</t>
+        </is>
+      </c>
+      <c r="AD29" s="13" t="n">
+        <v>0.46</v>
       </c>
       <c r="AE29" s="13" t="inlineStr">
         <is>
@@ -4787,7 +4977,7 @@
       </c>
       <c r="AF29" s="13" t="inlineStr">
         <is>
-          <t>Promoted ad-hoc from N019 (Sum=+4, flagged strongest signal). Two tranches: tranche 1 $198.10 @ $639.04 trailing buy fill 2026-04-17 00:02 UTC+8; tranche 2 $198.75 @ $641.14 limit fill 2026-04-17 00:13 UTC+8. Combined $396.85 USDT, avg entry $640.09. Reason for ad-hoc promotion: strongest NEW Sum+4 signal (TSM AI validation + NDX records + vol compression); blocking condition cleared overnight. Reconciled 2026-04-17.</t>
+          <t>Closed 2026-04-19 16:00 UTC+8 before Apr-22–23 earnings cluster. FOMC Apr-28 unresolved at exit.</t>
         </is>
       </c>
       <c r="AG29" s="13" t="inlineStr">
@@ -5864,6 +6054,192 @@
       <c r="AJ39" s="13" t="inlineStr">
         <is>
           <t>n/a (pre-meta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="P40" s="13" t="inlineStr">
+        <is>
+          <t>Stop hit at 95.000</t>
+        </is>
+      </c>
+      <c r="V40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="W40" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE40" s="13" t="inlineStr">
+        <is>
+          <t>trade-update-2026-04-20 (screenshot 15:03 UTC+8)</t>
+        </is>
+      </c>
+      <c r="AF40" s="13" t="inlineStr">
+        <is>
+          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~404.85 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20 (exact fill time unknown from screenshot).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>TSLAUSDT</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>395.56</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="P41" s="13" t="inlineStr">
+        <is>
+          <t>Stop hit at 400.000; TSLA Q1 earnings Apr-22 catalyst risk</t>
+        </is>
+      </c>
+      <c r="Q41" s="26" t="n">
+        <v>46134</v>
+      </c>
+      <c r="V41" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="W41" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE41" s="13" t="inlineStr">
+        <is>
+          <t>trade-update-2026-04-20 (screenshot 15:03 UTC+8)</t>
+        </is>
+      </c>
+      <c r="AF41" s="13" t="inlineStr">
+        <is>
+          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~394.08 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20. Stop 400.000 is only 1.12% above entry — very tight relative to ATR; risk of stop-tightening lesson replay. TSLA earnings Apr-22 = binary catalyst risk for short thesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>CLUSDT</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="P42" s="13" t="inlineStr">
+        <is>
+          <t>Stop hit at 85.300</t>
+        </is>
+      </c>
+      <c r="V42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="W42" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE42" s="13" t="inlineStr">
+        <is>
+          <t>trade-update-2026-04-20 (screenshot 17:07 UTC+8)</t>
+        </is>
+      </c>
+      <c r="AF42" s="13" t="inlineStr">
+        <is>
+          <t>Off-methodology long. No Sum score. Bybit Perp Cross 1x. Size ~395.47 USDT margin. Entered between 15:03 and 17:07 UTC+8 2026-04-20. Third CL entry this session (prior CLUSDT x2 in §7 batch log).</t>
         </is>
       </c>
     </row>
@@ -5881,7 +6257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -6287,6 +6663,84 @@
       <c r="P5" s="13" t="inlineStr">
         <is>
           <t>market-brief-2026-04-17 v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Risk-on / Reflation; geopolitical-fragile; ceasefire binary Apr-22 = primary unpriced tail</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>REFLATION</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>ON HOLD, hawkish tail</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>EASING</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>RISK-ON with geopolitical binary</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>NEGATIVE (most negative since 2023; squeeze setup)</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>S=0 (ActiveAddr 396k &lt; 400k threshold)</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Brent front-back curve + Iran ceasefire Apr-22</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>HY OAS 2.85% (financial conditions gate)</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>VIX/VIX3M 0.944 (vol term structure)</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>None (SPY |Sum|=+3 active; trade-rec to decide entry)</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="2"/>
@@ -11887,6 +12341,120 @@
       <c r="L16" s="13" t="inlineStr">
         <is>
           <t>catalysts-cache-2026-04-17.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Advance Retail Sales March</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SPY, QQQ, consumer</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Demand-side read post-energy shock; UMich prelim 47.6 suggests weak consumer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Iran ceasefire expires — no new talks scheduled; 3 sticking points unresolved</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brent, WTI, Gold, VIX, all risk assets</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PRIMARY BINARY — deal = Brent -5-10%; escalation = Brent +5-10%. Symmetric. Unpriced.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>46136</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>UMich final April sentiment (10am ET)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SPY, QQQ, DXY, consumer</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Prelim 47.6 record low (98% surveyed pre-ceasefire). Potential partial recovery if peace holds.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
         </is>
       </c>
     </row>
@@ -11910,7 +12478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -12262,6 +12830,78 @@
       </c>
       <c r="Q5" s="13" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Residual_Momentum_12stocks, Intermediary_Cap_Z, Basis_Mom_WTI_Gold_Silver_Copper</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>HY_OAS(T2), DGS2(T2 Apr-17), DFII10(T2 Apr-17), ACM_TP_10Y(monthly Jan-2026)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL (1/5 — Brent only)</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>DEGRADED (numpy compute failure blocks audit additions)</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-20/market-brief-2026-04-20.md v2</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>v2 production run. 35 T1 LIVE, 4 T2 web-search (HY_OAS/DGS2/DFII10/T10YIE). Audit-addition numpy failure — infrastructure fix needed.</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -1920,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -6240,6 +6240,727 @@
       <c r="AF42" s="13" t="inlineStr">
         <is>
           <t>Off-methodology long. No Sum score. Bybit Perp Cross 1x. Size ~395.47 USDT margin. Entered between 15:03 and 17:07 UTC+8 2026-04-20. Third CL entry this session (prior CLUSDT x2 in §7 batch log).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>696</v>
+      </c>
+      <c r="N43" t="n">
+        <v>720</v>
+      </c>
+      <c r="O43" t="n">
+        <v>730</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Break &lt;696 (2× ATR, below 50d MA)</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>v3 promoted half-size 1.0% due to 4 concurrent haircuts: IC z MISSING, FOMC Apr-29 tail, C=0, ceasefire spillover risk. Residual-mom numpy failure blocks all 11 single stocks; SPY/QQQ only non-T-blocked indices; QQQ correlation-blocked behind SPY.</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Non-stressed (proxies)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>N033</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>C/Corr</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Correlation-blocked behind SPY</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Near-miss: Sum +3 but correlation-gated (shared RISK-ON/equity theme). Re-evaluate if SPY closes.</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>N034</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Residual-mom MISSING (numpy)</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2 (T MISSING). 3rd test $75K support; F&amp;G 27; ETF -$325.8M; BTC/equity divergence widening.</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>N035</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Geopolitical premium partially unwound</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2. S/T pass; awaiting C catalyst (industrial surprise or Gold breakout).</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>N036</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ceasefire fragile; premium partial unwind</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2. Trigger: ceasefire breakdown → C=+1 → promote.</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>N037</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Oil direction conflict: Hormuz open vs cargo-seizure escalation</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2 (C=-1 conflict). Basis-momentum 4w +0.95 / 12w +2.95 steepening, no divergence cap.</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>N038</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Awaiting China PMI beat or fiscal stim</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2. S/T pass; catalyst pending.</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>N039</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NearMiss</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Risk-on/Reflation/Geo-fragile</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Awaiting KR macro catalyst</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2026-04-20/trade-rec-2026-04-20.md</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Near-miss Sum +2. Intl-equity sleeve ON (Faber gate). Catalyst-pending.</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>ALL 4 sleeves ON</t>
         </is>
       </c>
     </row>
@@ -11675,7 +12396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="2"/>
@@ -12351,32 +13072,32 @@
       <c r="B17" s="26" t="n">
         <v>46133</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Advance Retail Sales March</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>SPY, QQQ, consumer</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Demand-side read post-energy shock; UMich prelim 47.6 suggests weak consumer</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>2026-04-20/market-brief-2026-04-20.md v2</t>
         </is>
@@ -12389,32 +13110,32 @@
       <c r="B18" s="26" t="n">
         <v>46134</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Iran ceasefire expires — no new talks scheduled; 3 sticking points unresolved</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Brent, WTI, Gold, VIX, all risk assets</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>PRIMARY BINARY — deal = Brent -5-10%; escalation = Brent +5-10%. Symmetric. Unpriced.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>2026-04-20/market-brief-2026-04-20.md v2</t>
         </is>
@@ -12427,34 +13148,90 @@
       <c r="B19" s="26" t="n">
         <v>46136</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>UMich final April sentiment (10am ET)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>SPY, QQQ, DXY, consumer</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Prelim 47.6 record low (98% surveyed pre-ceasefire). Potential partial recovery if peace holds.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>2026-04-20/market-brief-2026-04-20.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Iran sanctions waiver expiry (SRE license)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Brent, WTI, SPY, energy, EM-EUR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Waiver renewal 50/50 base case</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NOT RENEWED</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>46131</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Bearish-oil / bullish-dollar outcome AVOIDED (waiver expired without renewal, no immediate tanker escalation); market read: contained escalation — crude bid partially faded on Apr-20 open.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SPY Long P009 (indirect — ceasefire-spillover risk offset); Brent N037 (direct)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NearMiss N037; Promoted P009</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-04-20/news-2026-04-20.md; 2026-04-20/trade-rec-2026-04-20.md v3</t>
         </is>
       </c>
     </row>
@@ -12918,7 +13695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="13" min="1" max="1"/>
@@ -14010,6 +14787,141 @@
       <c r="I24" s="13" t="inlineStr">
         <is>
           <t>trade-rec-2026-04-17.md v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V026 Residual momentum (12m FF5)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11 single stocks (NVDA/AAPL/AMZN/META/TSM/PLTR/INTC/TSLA/GOOGL/MU/AVGO)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MISSING (numpy not available in staging env)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BLANK</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Blocks T-leg for all 11 single-stock signals. Fail-loud: no silent-infer.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>YES — all single-stock promotions blocked</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-04-20/audit-data-staging-2026-04-20.md; 2026-04-20/trade-rec-2026-04-20.md v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V027 Intermediary Capital z-score</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cross-asset (R-overlay)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MISSING (numpy failure)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>R-leg forced to conditional/proxy mode. Proxies used: HY OAS 2.85% / NFCI -0.47 / VIX 19.36 — all non-stressed → R=+1 retained.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NO — proxies concur; SPY R=+1 retained with CONDITIONAL footnote</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-04-20/audit-data-staging-2026-04-20.md; 2026-04-20/trade-rec-2026-04-20.md v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V028 Basis-momentum (4w/12w)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brent (1/5 computed)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Brent +13.95 spread; 4w +0.95 / 12w +2.95 (steepening, aligned — no divergence cap)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No cap fires for Brent. WTI/Gold/Silver/Copper MISSING (numpy).</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-04-20/audit-data-staging-2026-04-20.md; 2026-04-20/trade-rec-2026-04-20.md v3</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -32,9 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -155,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +177,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6005,8 +6007,20 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>DISCRETIONARY_CLOSE</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>93.035</v>
+      </c>
+      <c r="Y40" s="16" t="n">
+        <v>46133</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-2.6388</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -6015,7 +6029,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~404.85 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20 (exact fill time unknown from screenshot).</t>
+          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~404.85 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20 (exact fill time unknown from screenshot). | CLOSED 2026-04-21 16:22 UTC+8 at 93.035 — discretionary close, adverse price. Realized -11.15 USDT (-2.79% incl fees).</t>
         </is>
       </c>
     </row>
@@ -6069,8 +6083,20 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>DISCRETIONARY_CLOSE</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>400.04505</v>
+      </c>
+      <c r="Y41" s="16" t="n">
+        <v>46132</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-1.1211</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -6079,7 +6105,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~394.08 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20. Stop 400.000 is only 1.12% above entry — very tight relative to ATR; risk of stop-tightening lesson replay. TSLA earnings Apr-22 = binary catalyst risk for short thesis.</t>
+          <t>Off-methodology short. No Sum score. Binance Perp Cross 1x. Size ~394.08 USDT margin. Entered &lt;=15:03 UTC+8 2026-04-20. Stop 400.000 is only 1.12% above entry — very tight relative to ATR; risk of stop-tightening lesson replay. TSLA earnings Apr-22 = binary catalyst risk for short thesis. | CLOSED 2026-04-20 20:49 UTC+8 at 400.04505 — discretionary close before TSLA earnings Apr-22. Realized -4.60 USDT (-1.17% incl fees).</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -2042,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="6" customWidth="1" style="15" min="1" max="1"/>
@@ -7106,6 +7106,768 @@
       <c r="AF50" t="inlineStr">
         <is>
           <t>ALL 4 sleeves ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86</v>
+      </c>
+      <c r="N51" t="n">
+        <v>95</v>
+      </c>
+      <c r="O51" t="n">
+        <v>98</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>USDJPY&lt;150; Nikkei -5%; BOJ emergency hike &gt;=50bp; US-China trade war escalation</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Promoted cloud-7pm 2026-04-21, re-confirmed local 20:20. Raw TSMOM (ETF). V027 z+1.65 (A). Size 0.75% corr haircut vs SPY.</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Intl Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Iran deal -&gt; rate hike risk -&gt; gold under pressure; break below $4640</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Commodity sleeve UNCERTAIN (GSCI MISSING 4th run) -&gt; effective OFF; Taken=NO</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>GATE-BLOCKED</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Sum+3 commodity gated. Gold $4808. Gate-blocked at local 20:20.</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Commodity UNCERTAIN/OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Iran ceasefire -&gt; commodity deflation; break below $75</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Commodity sleeve UNCERTAIN (GSCI MISSING 4th run) -&gt; effective OFF; Taken=NO</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>GATE-BLOCKED</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Sum+3 commodity gated. Silver $79.07. Gate-blocked at local 20:20.</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Commodity UNCERTAIN/OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>70</v>
+      </c>
+      <c r="M54" t="n">
+        <v>65</v>
+      </c>
+      <c r="N54" t="n">
+        <v>75</v>
+      </c>
+      <c r="O54" t="n">
+        <v>82</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Q1 miss on Terafab milestones/gross margin cut -&gt; C=0/-1 -&gt; exit; break below ATR stop; FOMC Apr-28-29 hawkish</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>NEW PROMOTION. V026 residual +13.89% (A) T=+1. Sum+4 highest conviction signal. Entry AFTER Apr-23 AC beat (Apr-24 morning). Size 1.0% full (V027 z+1.65 capital expansion). ATR ~$2.50.</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>273</v>
+      </c>
+      <c r="M55" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>280</v>
+      </c>
+      <c r="O55" t="n">
+        <v>290</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Break below $264 (2xATR); SPY break $696; FOMC hawkish; hard exit 2026-04-30 before May 1 earnings</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>NEW PROMOTION. V026 residual +4.68% T=+1. C=0 structural only. Size 0.75% corr haircut vs SPY. Hard time-stop 2026-04-30 BINDING.</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="n">
+        <v>335</v>
+      </c>
+      <c r="M56" t="n">
+        <v>317</v>
+      </c>
+      <c r="N56" t="n">
+        <v>355</v>
+      </c>
+      <c r="O56" t="n">
+        <v>375</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Earnings miss -&gt; Sum&lt;3 -&gt; no entry; break below 2xATR from entry; FOMC hawkish</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>CONTINGENT</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>CONTINGENT on Apr-23 UTC+8 beat confirm. V026 residual -0.80% T=0. Sum+3 via S+1/T0/C+1/R+1. Do not chase gap. Size 0.75%.</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>N040</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="R57" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Equity sleeve at capacity (SPY+EWJ+AAPL+INTC) during Apr-22-29 earnings+FOMC cluster</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>NEW. V026 residual +15.63% T=+1. Deferred to post-FOMC (Apr-30+). Trigger: position reduction allows entry.</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>N041</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Tech concentration (GOOGL+AAPL+INTC); T=0 (residual -1.00% neutral)</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>V026 residual -1.00% T=0 neutral. C+1 AI capex + GOOGL read-through. Trigger: GOOGL beat + residual &gt;+2%.</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Equity ON</t>
         </is>
       </c>
     </row>
@@ -14435,7 +15197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="21.06640625" customWidth="1" style="15" min="1" max="1"/>
@@ -15977,6 +16739,366 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>2026-04-21/meta-additions-staging-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;+1 (resid+13.89%)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>T=+1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>+1 Sum -&gt; new Sum+4 PROMOTED P013</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;+1 (resid+4.68%)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>T=+1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>+1 Sum -&gt; new Sum+3 PROMOTED P014</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;-1 (resid-35.62%)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>T=-1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-1 Sum -&gt; downgraded to +2 below threshold</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;-1 (resid-9.12%)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>T=-1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-1 Sum -&gt; confirmed no-trade</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;0 (resid-0.80%)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>T=0 resolved</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sum+3 confirmed via C+1 (no T change)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>V026 Residual Momentum</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T: MISSING-&gt;+1 (resid+15.63%)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>T=0 blocked</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>T=+1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>New Sum+3 near-miss N040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V027 IC z-score</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>All equity/intl</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>z: MISSING-&gt;+1.65 (fresh Apr-21)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R=+1 proxy-only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>R=+1 Grade A confirmed</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>R confidence upgraded; full sizing confirmed per Risk Rules 1.B</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MOVE (Bond Vol Index)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>All assets</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>67.90 (A fresh) was MISSING in cloud</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R=+1 HY OAS proxy</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>R=+1 Grade A triple (MOVE+HY+V027)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>R=+1 now Grade A confirmed across 3 independent inputs</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-04-21/trade-rec-2026-04-21.md</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -16,6 +16,7 @@
     <sheet name="PerformanceStats" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="README" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="MethodologyNotes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="HypoLedger" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DailyVariables'!$A$1:$BY$1</definedName>
@@ -32,12 +33,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="168" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -102,8 +105,33 @@
       <color rgb="FF375623"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -128,8 +156,38 @@
         <bgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF1"/>
+        <bgColor rgb="00DEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6D6D6"/>
+        <bgColor rgb="00D6D6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,11 +210,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,6 +251,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2036,6 +2147,1156 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" style="15" min="1" max="1"/>
+    <col width="12" customWidth="1" style="15" min="2" max="2"/>
+    <col width="30" customWidth="1" style="15" min="3" max="3"/>
+    <col width="8" customWidth="1" style="15" min="4" max="4"/>
+    <col width="10" customWidth="1" style="15" min="5" max="5"/>
+    <col width="5" customWidth="1" style="15" min="6" max="6"/>
+    <col width="5" customWidth="1" style="15" min="7" max="7"/>
+    <col width="5" customWidth="1" style="15" min="8" max="8"/>
+    <col width="5" customWidth="1" style="15" min="9" max="9"/>
+    <col width="5" customWidth="1" style="15" min="10" max="10"/>
+    <col width="16" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10" customWidth="1" style="15" min="12" max="12"/>
+    <col width="10" customWidth="1" style="15" min="13" max="13"/>
+    <col width="10" customWidth="1" style="15" min="14" max="14"/>
+    <col width="12" customWidth="1" style="15" min="15" max="15"/>
+    <col width="10" customWidth="1" style="15" min="16" max="16"/>
+    <col width="10" customWidth="1" style="15" min="17" max="17"/>
+    <col width="17" customWidth="1" style="15" min="18" max="18"/>
+    <col width="17" customWidth="1" style="15" min="19" max="19"/>
+    <col width="12" customWidth="1" style="15" min="20" max="20"/>
+    <col width="13" customWidth="1" style="15" min="21" max="21"/>
+    <col width="13" customWidth="1" style="15" min="22" max="22"/>
+    <col width="13" customWidth="1" style="15" min="23" max="23"/>
+    <col width="13" customWidth="1" style="15" min="24" max="24"/>
+    <col width="72" customWidth="1" style="15" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="15">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>H_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Rec_Date</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Rec_File</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>Entry_Price_Rec</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
+        <is>
+          <t>Stop_Rec</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t>TP1_Rec</t>
+        </is>
+      </c>
+      <c r="N1" s="19" t="inlineStr">
+        <is>
+          <t>TP2_Rec</t>
+        </is>
+      </c>
+      <c r="O1" s="19" t="inlineStr">
+        <is>
+          <t>Inv_Date</t>
+        </is>
+      </c>
+      <c r="P1" s="19" t="inlineStr">
+        <is>
+          <t>Size_Rec_%</t>
+        </is>
+      </c>
+      <c r="Q1" s="19" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>Hypo_Entry_Price</t>
+        </is>
+      </c>
+      <c r="S1" s="19" t="inlineStr">
+        <is>
+          <t>Hypo_Current_Price</t>
+        </is>
+      </c>
+      <c r="T1" s="19" t="inlineStr">
+        <is>
+          <t>Hypo_PnL_%</t>
+        </is>
+      </c>
+      <c r="U1" s="19" t="inlineStr">
+        <is>
+          <t>Actual_Taken</t>
+        </is>
+      </c>
+      <c r="V1" s="19" t="inlineStr">
+        <is>
+          <t>Actual_Entry</t>
+        </is>
+      </c>
+      <c r="W1" s="19" t="inlineStr">
+        <is>
+          <t>Actual_Exit</t>
+        </is>
+      </c>
+      <c r="X1" s="19" t="inlineStr">
+        <is>
+          <t>Actual_PnL_%</t>
+        </is>
+      </c>
+      <c r="Y1" s="19" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>H001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-15 v3</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="L2" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="M2" s="21" t="n">
+        <v>156</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>166</v>
+      </c>
+      <c r="O2" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="P2" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="Q2" s="23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="S2" s="21" t="n">
+        <v>152.33</v>
+      </c>
+      <c r="T2" s="24">
+        <f>(S2-R2)/R2</f>
+        <v/>
+      </c>
+      <c r="U2" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V2" s="21" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="W2" s="21" t="n">
+        <v>145.39</v>
+      </c>
+      <c r="X2" s="22" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="Y2" s="25" t="inlineStr">
+        <is>
+          <t>Actual stop moved too tight (~breakeven). Methodology stop $133 never hit. Hypo at rec midpoint $146 still open. Current $152.33 (Apr-21). Hypo +4.34% vs actual +0.92%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>H002</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-15 v2-&gt;v3</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="20" t="n"/>
+      <c r="L3" s="20" t="n"/>
+      <c r="M3" s="20" t="n"/>
+      <c r="N3" s="20" t="n"/>
+      <c r="O3" s="20" t="n"/>
+      <c r="P3" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q3" s="26" t="inlineStr">
+        <is>
+          <t>VOIDED</t>
+        </is>
+      </c>
+      <c r="R3" s="20" t="n"/>
+      <c r="S3" s="20" t="n"/>
+      <c r="T3" s="20" t="n"/>
+      <c r="U3" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V3" s="20" t="n"/>
+      <c r="W3" s="20" t="n"/>
+      <c r="X3" s="20" t="n"/>
+      <c r="Y3" s="25" t="inlineStr">
+        <is>
+          <t>Promoted in v2 (residual +20.6%), de-promoted in v3 same session (residual flipped to -19.78%; T: +1-&gt;-1). No actionable entry window. Rec note: "P002 in the hypo-ledger must be annotated."</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>H003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-15 v3</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="L4" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="P4" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="S4" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="T4" s="24">
+        <f>(S4-R4)/R4</f>
+        <v/>
+      </c>
+      <c r="U4" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V4" s="21" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="W4" s="21" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="X4" s="22" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="Y4" s="25" t="inlineStr">
+        <is>
+          <t>Actual exited early Apr-19 at $68.26 before Apr-23 earnings. Hypo at rec midpoint $62 still open (stop $56, inv May-13). Current ~$68 -&gt; hypo +9.68% vs actual +2.09%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>H004</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-16 v3</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>4830</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>4640</v>
+      </c>
+      <c r="M5" s="21" t="n">
+        <v>4990</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>5140</v>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="n">
+        <v>4830</v>
+      </c>
+      <c r="S5" s="21" t="n">
+        <v>4808</v>
+      </c>
+      <c r="T5" s="24">
+        <f>(S5-R5)/R5</f>
+        <v/>
+      </c>
+      <c r="U5" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V5" s="21" t="n">
+        <v>4780.69</v>
+      </c>
+      <c r="W5" s="21" t="n">
+        <v>4823.65</v>
+      </c>
+      <c r="X5" s="22" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Y5" s="25" t="inlineStr">
+        <is>
+          <t>Actual exited early Apr-18 before Iran ceasefire binary (Apr-22). Hypo at zone midpoint $4,830. Current $4,808 (-0.46%). Stop $4,640 not hit; inv May-14. Actual +0.80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>H005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-16 v3</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>597</v>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q6" s="27" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="S6" s="21" t="n">
+        <v>646.79</v>
+      </c>
+      <c r="T6" s="24">
+        <f>(S6-R6)/R6</f>
+        <v/>
+      </c>
+      <c r="U6" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V6" s="21" t="n">
+        <v>640.09</v>
+      </c>
+      <c r="W6" s="21" t="n">
+        <v>643.02</v>
+      </c>
+      <c r="X6" s="22" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="Y6" s="25" t="inlineStr">
+        <is>
+          <t>Flagged Sum+4 in rec but not formally promoted (correlation gate cautionary). Gerald entered Apr-17 at avg $640.09; exited Apr-19 at $643.02 (+1.13%). Hypo at Apr-16 brief price $637.40, current $646.79 (+1.47%). Stop $597 not hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>H006</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-20 v3</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>696</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>720</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>730</v>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="P7" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="S7" s="21" t="n">
+        <v>706</v>
+      </c>
+      <c r="T7" s="24">
+        <f>(S7-R7)/R7</f>
+        <v/>
+      </c>
+      <c r="U7" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V7" s="21" t="n">
+        <v>710.17</v>
+      </c>
+      <c r="W7" s="20" t="n"/>
+      <c r="X7" s="20" t="n"/>
+      <c r="Y7" s="25" t="inlineStr">
+        <is>
+          <t>Actual filled avg $710.17 (4 tranches Apr-21). Open. Current ~$706 (Apr-22 09:23) -&gt; hypo -0.58%. Stop $696 not hit. Half-size: C=0 + IC z MISSING at rec time + FOMC Apr-28 tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>H007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-21 v2</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>95</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>98</v>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="S8" s="21" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="T8" s="24">
+        <f>(S8-R8)/R8</f>
+        <v/>
+      </c>
+      <c r="U8" s="20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V8" s="21" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="W8" s="20" t="n"/>
+      <c r="X8" s="20" t="n"/>
+      <c r="Y8" s="25" t="inlineStr">
+        <is>
+          <t>Actual filled avg $88.44 (~2.2% below rec estimate $90.24). Open. Current ~$89.18 (Apr-22) -&gt; hypo -1.17% / actual +0.84%. Stop $86 not hit; inv Jun-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>H008</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-21 v2</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P9" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q9" s="28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="R9" s="20" t="n"/>
+      <c r="S9" s="20" t="n"/>
+      <c r="T9" s="20" t="n"/>
+      <c r="U9" s="20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="n"/>
+      <c r="W9" s="20" t="n"/>
+      <c r="X9" s="20" t="n"/>
+      <c r="Y9" s="25" t="inlineStr">
+        <is>
+          <t>P013. Entry AFTER Apr-23 AC beat confirmation (~$68-72 limit). Sum+4 -- highest conviction. Terafab foundry validation thesis. Entry gate: INTC beat + Terafab milestone. Inv 2026-06-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>H009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-21 v2</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>265.75</v>
+      </c>
+      <c r="M10" s="21" t="n">
+        <v>280</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>290</v>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P10" s="22" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q10" s="28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="R10" s="20" t="n"/>
+      <c r="S10" s="20" t="n"/>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="V10" s="20" t="n"/>
+      <c r="W10" s="20" t="n"/>
+      <c r="X10" s="20" t="n"/>
+      <c r="Y10" s="25" t="inlineStr">
+        <is>
+          <t>P014. Limit ~$271-274. Stop ~$264-267 (2x ATR). HARD time-stop 2026-04-30 -- MUST exit before May-1 earnings. C=0; edge is structural momentum only. In zone at $273 (Apr-22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>H010</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-21 v2</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>317</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>355</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>375</v>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q11" s="28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="R11" s="20" t="n"/>
+      <c r="S11" s="20" t="n"/>
+      <c r="T11" s="20" t="n"/>
+      <c r="U11" s="20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="V11" s="20" t="n"/>
+      <c r="W11" s="20" t="n"/>
+      <c r="X11" s="20" t="n"/>
+      <c r="Y11" s="25" t="inlineStr">
+        <is>
+          <t>P015. Entry AFTER Apr-23 UTC+8 beat confirmation (~$333-340 limit). T=0 (residual -0.80%, within +/-2% zero band). Do not chase gap. Inv 2026-05-15. Contingent on beat: miss -&gt; no entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>PERFORMANCE SUMMARY (auto-updated by signal-review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Formally Promoted (OPEN+PENDING+FLAGGED)</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>COUNTIF(Q2:Q11,"OPEN")+COUNTIF(Q2:Q11,"PENDING")+COUNTIF(Q2:Q11,"FLAGGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>OPEN (marked-to-market)</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>COUNTIF(Q2:Q11,"OPEN")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>PENDING (entry trigger)</t>
+        </is>
+      </c>
+      <c r="B16" s="31">
+        <f>COUNTIF(Q2:Q11,"PENDING")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>VOIDED (de-promoted same session)</t>
+        </is>
+      </c>
+      <c r="B17" s="31">
+        <f>COUNTIF(Q2:Q11,"VOIDED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>FLAGGED (Sum&gt;=3, not formally promoted)</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
+        <f>COUNTIF(Q2:Q11,"FLAGGED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Hypo Avg PnL% -- OPEN signals</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>AVERAGEIF(Q2:Q11,"OPEN",T2:T11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Actual Avg PnL% -- closed YES</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>AVERAGEIFS(X2:X11,U2:U11,"YES",W2:W11,"&lt;&gt;"&amp;"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Last updated</t>
+        </is>
+      </c>
+      <c r="B21" s="31">
+        <f>TEXT(NOW(),"YYYY-MM-DD HH:MM UTC+8")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:H13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6374,8 +7635,20 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
+          <t>DISCRETIONARY_CLOSE</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="Y42" s="18" t="n">
+        <v>46133</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.31</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -6384,7 +7657,7 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Off-methodology long. No Sum score. Bybit Perp Cross 1x. Size ~395.47 USDT margin. Entered between 15:03 and 17:07 UTC+8 2026-04-20. Third CL entry this session (prior CLUSDT x2 in §7 batch log).</t>
+          <t>Off-methodology long. No Sum score. Bybit Perp Cross 1x. Size ~395.47 USDT margin. Entered between 15:03 and 17:07 UTC+8 2026-04-20. Third CL entry this session (prior CLUSDT x2 in §7 batch log). | CLOSED DISCRETIONARY 2026-04-21 23:10 UTC+8 @ 88.52 avg. Realized +/usr/bin/bash.79 (+0.19%). Small profit exit; P009/P010 open.</t>
         </is>
       </c>
     </row>
@@ -6433,7 +7706,7 @@
         <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>710.14</v>
+        <v>708.95</v>
       </c>
       <c r="M43" t="n">
         <v>696</v>
@@ -6464,7 +7737,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6484,7 +7757,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>ALL 4 sleeves ON</t>
+          <t>ALL 4 sleeves ON. FILLED 2026-04-21 21:43-22:14 UTC+8: T1 397.43 USDT@709.70 (21:43), T2 397.35@709.56 (21:44), T3 398.12@710.93 market (22:13), T4 199.05@710.90 (22:14). Total 1391.96 USDT, avg 710.17, 1.960 units. Stop 696.00. | T5 added 2026-04-22 05:04:47 UTC+8: 699.445 USDT @ 706.51 (Limit). Total 2089.08 USDT, avg 708.95.</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -7154,7 +8427,7 @@
         <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>90.23999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="M51" t="n">
         <v>86</v>
@@ -7185,7 +8458,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7200,7 +8473,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Promoted cloud-7pm 2026-04-21, re-confirmed local 20:20. Raw TSMOM (ETF). V027 z+1.65 (A). Size 0.75% corr haircut vs SPY.</t>
+          <t>Promoted cloud-7pm 2026-04-21, re-confirmed local 20:20. Raw TSMOM (ETF). V027 z+1.65 (A). Size 0.75% corr haircut vs SPY. FILLED 2026-04-21 21:47-22:13 UTC+8: T1 799.02 USDT@88.48 market (21:47), T2 399.55@88.39 market (22:13). Two limit orders @88.42 cancelled before fills. Total 1198.57 USDT, avg 88.44, 13.551 units. Stop 86.00. Entry better than rec estimate 90.24 — filled ~2% below plan. | T3 added 2026-04-22 05:07:30 UTC+8: 199.249 USDT @ 87.39 (Market). Total 1396.05 USDT, avg 88.30.</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="168" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -129,6 +129,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -228,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,6 +293,7 @@
     <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18970,7 +18974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="25" customWidth="1" style="15" min="1" max="1"/>
@@ -19053,7 +19057,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>All promoted and near-miss signals. Mirrors hypo-ledger-2026.md in structured form.</t>
+          <t>All promoted and near-miss signals. Append-only ledger — one row per signal.</t>
         </is>
       </c>
     </row>
@@ -19260,163 +19264,196 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="6" t="n"/>
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>HypoLedger</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>All formally promoted signals (Sum&gt;=3, checklist PASS) tracked at recommendation price for system efficacy measurement.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Producer: daily-trade-rec skill Step 8.5 (appends H### rows at rec time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="15">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Consumer: signal-review (marks to market weekly, produces dim-14 efficacy report in PerformanceStats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="15">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Key columns: H_ID, Rec_Date, Asset, Direction, Entry_Price_Rec, Stop_Rec, TP1_Rec, Hypo_Entry_Price, Hypo_Current_Price, Hypo_PnL_%, Actual_Taken, Actual_PnL_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="15">
+      <c r="A43" s="6" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="15">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>RULES:</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>1. SignalLedger is append-only. Never delete or retroactively edit rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>2. DailyVariables: one row per trading day. Overwrite only if same-day correction (note in Source_Brief).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="15">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>3. VariableRegistry: variables can change status but are never deleted. Rejected/Retired variables stay for audit trail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="15">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>4. Markdown files remain the human-readable presentation layer. This workbook is the analytical layer.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>5. If markdown and Excel diverge, Excel is source of truth for quantitative data.</t>
+          <t>1. SignalLedger is append-only. Never delete or retroactively edit rows.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="15">
-      <c r="A46" s="6" t="n"/>
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>2. DailyVariables: one row per trading day. Overwrite only if same-day correction (note in Source_Brief).</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="15">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>VARIABLE DISCOVERY SYSTEM:</t>
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>3. VariableRegistry: variables can change status but are never deleted. Rejected/Retired variables stay for audit trail.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
       <c r="A48" s="11" t="inlineStr">
         <is>
+          <t>4. Markdown files remain the human-readable presentation layer. This workbook is the analytical layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="15">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>5. If markdown and Excel diverge, Excel is source of truth for quantitative data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="15">
+      <c r="A50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="15">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>VARIABLE DISCOVERY SYSTEM:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="15">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>Status Ladder:</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Candidate — plausible idea, not yet assessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="15">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Watchlist — weak or mixed evidence, worth tracking over time</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Under Review — being actively assessed with data</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="15">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Provisionally Useful — seems helpful but not fully trusted (pilot phase)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="15">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Approved — good enough for regular use, pending Grade A evidence</t>
+          <t xml:space="preserve">  Candidate — plausible idea, not yet assessed</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="15">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Grade A — strong evidence, repeated usefulness, in core methodology</t>
+          <t xml:space="preserve">  Watchlist — weak or mixed evidence, worth tracking over time</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="15">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rejected — failed screening or proved unhelpful; kept for audit trail</t>
+          <t xml:space="preserve">  Under Review — being actively assessed with data</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="15">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Retired — was useful but no longer (regime change, decay, etc.)</t>
+          <t xml:space="preserve">  Provisionally Useful — seems helpful but not fully trusted (pilot phase)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="15">
-      <c r="A57" s="6" t="n"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Approved — good enough for regular use, pending Grade A evidence</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="15">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>Review Cadence:</t>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Grade A — strong evidence, repeated usefulness, in core methodology</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Daily: literature-review and market-brief can add Candidate entries</t>
+          <t xml:space="preserve">  Rejected — failed screening or proved unhelpful; kept for audit trail</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="15">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Weekly: signal-review flags blocking patterns that suggest variable gaps</t>
+          <t xml:space="preserve">  Retired — was useful but no longer (regime change, decay, etc.)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Monthly: bootstrap-review and quarterly-review assess Watchlist promotions</t>
-        </is>
-      </c>
+      <c r="A61" s="6" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="15">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Quarterly: formal promote/demote/reject decisions with Gerald sign-off</t>
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Review Cadence:</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="15">
       <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Daily: literature-review and market-brief can add Candidate entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Weekly: signal-review flags blocking patterns that suggest variable gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Monthly: bootstrap-review and quarterly-review assess Watchlist promotions</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Quarterly: formal promote/demote/reject decisions with Gerald sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Semi-annual: literature-review deep scan for new academic variables</t>
         </is>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -2384,7 +2384,7 @@
         <v>146</v>
       </c>
       <c r="S2" s="21" t="n">
-        <v>152.33</v>
+        <v>150.09</v>
       </c>
       <c r="T2" s="24">
         <f>(S2-R2)/R2</f>
@@ -2551,7 +2551,7 @@
         <v>62</v>
       </c>
       <c r="S4" s="21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T4" s="24">
         <f>(S4-R4)/R4</f>
@@ -2647,7 +2647,7 @@
         <v>4830</v>
       </c>
       <c r="S5" s="21" t="n">
-        <v>4808</v>
+        <v>4785.16</v>
       </c>
       <c r="T5" s="24">
         <f>(S5-R5)/R5</f>
@@ -2835,7 +2835,7 @@
         <v>710.14</v>
       </c>
       <c r="S7" s="21" t="n">
-        <v>706</v>
+        <v>706.14</v>
       </c>
       <c r="T7" s="24">
         <f>(S7-R7)/R7</f>
@@ -3198,6 +3198,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -134,7 +134,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -189,6 +189,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -231,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,6 +300,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2157,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="15" min="1" max="1"/>
@@ -3198,106 +3206,278 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>H011</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-16 v3</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="34" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="L12" s="34" t="n">
+        <v>297</v>
+      </c>
+      <c r="M12" s="34" t="n">
+        <v>360</v>
+      </c>
+      <c r="N12" s="34" t="n">
+        <v>380</v>
+      </c>
+      <c r="O12" s="34" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="P12" s="34" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q12" s="34" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="R12" s="34" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="S12" s="34" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="T12" s="34">
+        <f>(S12-R12)/R12</f>
+        <v/>
+      </c>
+      <c r="U12" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V12" s="34" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="34" t="n"/>
+      <c r="Y12" s="34" t="inlineStr">
+        <is>
+          <t>Flagged Sum+3 Apr-16 (residual +30.52%, T unblocked). Not promoted: correlation gate (EWY+INTC+GOOGL equity heat ~13.75%) + post-rally entry risk (+6.01% same day) + FOMC Apr-28 timing. Earnings Apr-22 now past. H010 = Apr-21 PENDING re-entry (post-earnings contingent).</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>H012</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-16 v3</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="34" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="L13" s="34" t="n">
+        <v>685</v>
+      </c>
+      <c r="M13" s="34" t="n">
+        <v>720</v>
+      </c>
+      <c r="N13" s="34" t="n">
+        <v>740</v>
+      </c>
+      <c r="O13" s="34" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="P13" s="34" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q13" s="34" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="R13" s="34" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="S13" s="34" t="n">
+        <v>706.14</v>
+      </c>
+      <c r="T13" s="34">
+        <f>(S13-R13)/R13</f>
+        <v/>
+      </c>
+      <c r="U13" s="34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="V13" s="34" t="n"/>
+      <c r="W13" s="34" t="n"/>
+      <c r="X13" s="34" t="n"/>
+      <c r="Y13" s="34" t="inlineStr">
+        <is>
+          <t>Flagged Sum+3 Apr-16. Not promoted: dominated by open QQQ position (same broad equity risk-on regime variable). Apr-17 rec explicitly blocks via correlation gate (Risk Rules §5 item 3). Formally promoted 4 days later at $710.14 (H006 Apr-20). Counterfactual: Apr-16 FLAGGED entry $699.94 vs Apr-20 formal entry $710.14 = $10.20/share better entry. Hypo +0.89% vs H006 hypo -0.56% as of Apr-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>PERFORMANCE SUMMARY (auto-updated by signal-review)</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>Formally Promoted (OPEN+PENDING+FLAGGED)</t>
-        </is>
-      </c>
-      <c r="B14" s="31">
-        <f>COUNTIF(Q2:Q11,"OPEN")+COUNTIF(Q2:Q11,"PENDING")+COUNTIF(Q2:Q11,"FLAGGED")</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>OPEN (marked-to-market)</t>
+          <t>Formally Promoted (OPEN+PENDING+FLAGGED)</t>
         </is>
       </c>
       <c r="B15" s="31">
-        <f>COUNTIF(Q2:Q11,"OPEN")</f>
+        <f>COUNTIF(Q2:Q13,"OPEN")+COUNTIF(Q2:Q13,"PENDING")+COUNTIF(Q2:Q13,"FLAGGED")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>PENDING (entry trigger)</t>
+          <t>OPEN (marked-to-market)</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>COUNTIF(Q2:Q11,"PENDING")</f>
+        <f>COUNTIF(Q2:Q13,"OPEN")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>VOIDED (de-promoted same session)</t>
+          <t>PENDING (entry trigger)</t>
         </is>
       </c>
       <c r="B17" s="31">
-        <f>COUNTIF(Q2:Q11,"VOIDED")</f>
+        <f>COUNTIF(Q2:Q13,"PENDING")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>FLAGGED (Sum&gt;=3, not formally promoted)</t>
+          <t>VOIDED (de-promoted same session)</t>
         </is>
       </c>
       <c r="B18" s="31">
-        <f>COUNTIF(Q2:Q11,"FLAGGED")</f>
+        <f>COUNTIF(Q2:Q13,"VOIDED")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Hypo Avg PnL% -- OPEN signals</t>
-        </is>
-      </c>
-      <c r="B19" s="32">
-        <f>AVERAGEIF(Q2:Q11,"OPEN",T2:T11)</f>
+          <t>FLAGGED (Sum&gt;=3, not formally promoted)</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
+        <f>COUNTIF(Q2:Q13,"FLAGGED")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>Actual Avg PnL% -- closed YES</t>
+          <t>Hypo Avg PnL% -- OPEN signals</t>
         </is>
       </c>
       <c r="B20" s="32">
-        <f>AVERAGEIFS(X2:X11,U2:U11,"YES",W2:W11,"&lt;&gt;"&amp;"")</f>
+        <f>AVERAGEIF(Q2:Q13,"OPEN",T2:T13)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
+          <t>Actual Avg PnL% -- closed YES</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>AVERAGEIFS(X2:X13,U2:U13,"YES",W2:W13,"&lt;&gt;"&amp;"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
           <t>Last updated</t>
         </is>
       </c>
-      <c r="B21" s="31">
+      <c r="B22" s="31">
         <f>TEXT(NOW(),"YYYY-MM-DD HH:MM UTC+8")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A13:H13"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -1987,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="15" min="1" max="1"/>
@@ -2151,6 +2151,56 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>Shadow mode Mon-Fri 2026-04-20..04-24. Review fires 2026-04-25 10:00 UTC+8. V030 MISSING until subscription confirmed; V031/V032 stub-only pending Phase 2b self-compute implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MetaIntegration-PostAudit-Patch</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-22 post-integration audit of Methodology Prompt: 7 targeted changes. (1) V036 PCTECH added as T-group index-sleeve input — Neely-Rapach-Tu-Zhou 2014 MgmtSci; PL-NMA rank 9/54, BNMA DEPLOY_CONDITIONAL. (2) V030 DealerGamma citation corrected from Barbon-Buraschi (2021) — wrong paper, never in SR corpus — to Baltussen-Da-Lammers-Martens 2021 JFE + Zhu et al. 2024. (3) V014 BTC netflows construct-split note added (order-flow sub-construct tradable; vol-sort sub-construct EXCLUDE until separated). (4) V020 VRP operational note — DEPLOY_CONDITIONAL per SR (6 reviews, consensus 0.83) but held monitoring-only pending GWZ 2024 decay resolution. (5) V016 BTC funding PL-NMA vs BNMA contradiction documented; BNMA EXCLUDE verdict stands. (6) HMLDevil added to WATCH registry (gate: 3+ papers + post-2022 OOS). (7) New Systematic Review WATCH List section with 7 tracked candidates (HMLDevil, QMJ, OppInsider, LazyPrices, ADS_Nowcast, LM_Text, CieslakPovala) — explicit 2026-10-14 re-evaluation mandate.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Methodology Prompt.md; bnma/meta-analysis/meta_results.json; bnma/meta-analysis/pl_nma_results.json; bnma/meta-analysis/BNMA-meta-analysis-2026-04-18.md</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VariableRegistry (V030 citation corrected row 31; V036 appended); MethodologyNotes (this row)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>V030 (citation); V036 (new); V014 (construct-split note); V020 (operational note); V016 (contradiction note); HMLDevil+6 watchlist variables (registered)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Executed on delegated run approval (2026-04-22 session)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Manual operator + post-integration audit</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Architecture v6 registry remains authoritative at V001-V035 (immutable per governance); V036 lives in Methodology Prompt + this sheet only until next architecture version. Downstream propagation: Trad core.md §30 citation corrected; scripts/compute_meta_additions.py line 218 grade string corrected. Dated files under 2026-04-XX/ NOT retroactively edited (paper trail). V036 data pipeline not yet scheduled — Phase 2 work gated on separate approval.</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -14000,7 +14050,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Barbon-Buraschi (2021) single-paper</t>
+          <t>Baltussen-Da-Lammers-Martens (2021) JFE 142(1) "Hedging Demand and Market Intraday Momentum"; Zhu et al. (2024) SPY extension (net Sharpe 1.33)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -14070,7 +14120,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Added 2026-04-18 via meta-integration. Data subscription pending Gerald decision — rows MISSING in shadow mode. Review Grade at 2026-07-01.</t>
+          <t>Added 2026-04-18 via meta-integration. Data subscription pending Gerald decision — rows MISSING in shadow mode. Review Grade at 2026-07-01. | 2026-04-22: Source_Paper corrected from "Barbon-Buraschi (2021) single-paper" (wrong paper, never in systematic-review corpus) to Baltussen-Da-Lammers-Martens 2021 JFE per meta_results.json audit.</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -14080,7 +14130,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Grade B — single paper. Review at 2026-07-01 quarterly. Subscription unconfirmed 2026-04-18; rows stay MISSING until resolved.</t>
+          <t>Grade B — single paper. Review at 2026-07-01 quarterly. Subscription unconfirmed 2026-04-18; rows stay MISSING until resolved. [2026-04-22 citation correction: operational anchor is Baltussen et al. 2021 JFE; Grade B status unchanged.]</t>
         </is>
       </c>
     </row>
@@ -14816,6 +14866,163 @@
       <c r="AJ36" t="inlineStr">
         <is>
           <t>Crypto sleeve gate. ETH inherits BTC sleeve status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PCTECH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Neely-Rapach PC-TECH composite — principal components of 14 technical indicators forecasting equity risk premium</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Equities (Index: SPY/QQQ)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Technical/Timing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scoring (Index T-leg)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Grade B</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Shadow (registered 2026-04-22, data pipeline pending)</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>46134</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meta-analysis 2026-04-18 (BNMA + PL-NMA); registered to Methodology Prompt 2026-04-22 after gap identified in post-integration audit</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Neely, Rapach, Tu, Zhou (2014) Management Science 60(7) 1772-1791 "Forecasting the Equity Risk Premium: The Role of Technical Indicators"</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>PC composite of MA crossovers / momentum / volume indicators — captures technical signal independent of TSMOM</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>PARTIAL (Goyal-Welch-Zafirov 2024 qualitative survival; no second formal replication)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>PASS (distinct horizon/signal family from V009 TSMOM)</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>PASS (monthly data; free sources)</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="U37" t="n">
+        <v>40</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0.30-0.45</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Low with V009 TSMOM (different horizon/signal family) — use as second T-leg on index sleeve only</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>NOT redundant with V009 on indices; redundant on single stocks (do not score V036 on single-stock sleeve)</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Amit Goyal replication archive OR self-compute from 14 technical indicators</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>0-5d</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>V009 + V036 on same index ticker: average, do not sum (Methodology Prompt scoring rule #5, 2026-04-22)</t>
+        </is>
+      </c>
+      <c r="AC37" s="17" t="n">
+        <v>46134</v>
+      </c>
+      <c r="AD37" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Registered 2026-04-22 via post-integration audit. PL-NMA rank 9/54 primary, 6/54 S2 (robust-top-10); BNMA post_mean 0.484, prob_positive 1.0. Phase-2 data pipeline not yet scheduled.</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Not yet assessed (shadow — no live rows yet)</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>DEPLOY_CONDITIONAL per systematic review. Flag Grade B in every brief referencing it. Second independent replication required for Grade A promotion at 2026-10-14.</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -2216,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="11.9296875" customWidth="1" style="33" min="1" max="1"/>
@@ -3423,96 +3423,172 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H013</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>trade-rec-2026-04-22 v1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>102</v>
+      </c>
+      <c r="O14" s="34" t="n">
+        <v>46164</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Commodity sleeve CONFIRMED ON first time; primary post-gate promotion; corr+binary haircut 0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>PERFORMANCE SUMMARY (auto-updated by signal-review)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Formally Promoted (OPEN+PENDING+FLAGGED)</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B16" s="27">
         <f>COUNTIF(Q2:Q13,"OPEN")+COUNTIF(Q2:Q13,"PENDING")+COUNTIF(Q2:Q13,"FLAGGED")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>OPEN (marked-to-market)</t>
         </is>
       </c>
-      <c r="B16" s="27">
+      <c r="B17" s="27">
         <f>COUNTIF(Q2:Q13,"OPEN")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>PENDING (entry trigger)</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B18" s="27">
         <f>COUNTIF(Q2:Q13,"PENDING")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>VOIDED (de-promoted same session)</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B19" s="27">
         <f>COUNTIF(Q2:Q13,"VOIDED")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>FLAGGED (Sum&gt;=3, not formally promoted)</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B20" s="27">
         <f>COUNTIF(Q2:Q13,"FLAGGED")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Hypo Avg PnL% -- OPEN signals</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B21" s="28">
         <f>AVERAGEIF(Q2:Q13,"OPEN",T2:T13)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Actual Avg PnL% -- closed YES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B22" s="28">
         <f>AVERAGEIFS(X2:X13,U2:U13,"YES",W2:W13,"&lt;&gt;"&amp;"")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Last updated</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B23" s="27">
         <f>TEXT(NOW(),"YYYY-MM-DD HH:MM UTC+8")</f>
         <v/>
       </c>
@@ -3528,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="6" customWidth="1" style="33" min="1" max="1"/>
@@ -9367,6 +9443,652 @@
       <c r="AG58" t="inlineStr">
         <is>
           <t>Equity ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="M59" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N59" t="n">
+        <v>98</v>
+      </c>
+      <c r="O59" t="n">
+        <v>102</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Iran deal confirmed -&gt; Brent &lt;$88; Hormuz re-opens shipping &gt;70% normal within 10d</t>
+        </is>
+      </c>
+      <c r="Q59" s="34" t="n">
+        <v>46164</v>
+      </c>
+      <c r="R59" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Commodity sleeve CONFIRMED ON first time (V034 GSG 31.75 &gt; 10m-SMA 25.35). Primary commodity promotion post-gate. Size 0.75% (corr+binary haircut + TSLA earnings tonight cross-asset risk + FOMC Apr-28 tail). PARTIAL checklist #6 (C=0, structural edge only) - same precedent as P009 SPY half-size.</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>n/a (commodity)</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>n/a (commodity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Promoted</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Active addr &lt;400k (structural S collapse); BTC &lt;$75k 5th support test break</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>OverlayGateOff (Crypto sleeve OFF - BTC $78,357 &lt; 10m-SMA $91,523)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>GATE-BLOCKED</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>S flipped 0-&gt;+1 on active addresses 478,903 &gt; 400K threshold. Crypto sleeve OFF per V035 Faber 10m-SMA. Next gate review May-01 (Apr-30 close). BTC needs +17.1% to $91.5k for gate ON.</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>N042</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C61" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="R61" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Corr+STALE_T3</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Correlation-blocked behind Brent + basis-mom T3 STALE Apr-17 at 5d limit. Would promote if Brent fails or fresh WTI basis-mom lands non-divergent.</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>N043</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Corr</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Gate-UNBLOCKED today (sleeve CONFIRMED ON) but correlation-gated behind Brent. Promotes if Brent fills + sector cap has room, or industrial-surprise C+1.</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>N044</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>China PMI &gt;50.5 needed. Next print May-01. Correlation-gate also behind Brent within commodity sector cap.</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>N045</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Equity-single</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Residual +2.38% (borderline T+1); no near-term catalyst. Re-evaluate at AI/data-center news flow or earnings.</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>N046</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Near-Miss</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Equity-single</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>RISK-ON (FRAGILE) / GEOPOLITICAL-BINARY - CEASEFIRE EXTENDED, HORMUZ BLOCKED</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>2026-04-22/trade-rec-2026-04-22.md</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Residual -1.00% (T=0); raw TSMOM +53.55% (trust residual per methodology). C+1 for GOOGL Apr-29 AI read-through. Promotes if residual flips &gt;+2%.</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Equity:ON Intl:ON Commodity:ON Crypto:OFF</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>CapitalExpansion(+1.65)</t>
         </is>
       </c>
     </row>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -9520,7 +9520,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Commodity sleeve CONFIRMED ON first time (V034 GSG 31.75 &gt; 10m-SMA 25.35). Primary commodity promotion post-gate. Size 0.75% (corr+binary haircut + TSLA earnings tonight cross-asset risk + FOMC Apr-28 tail). PARTIAL checklist #6 (C=0, structural edge only) - same precedent as P009 SPY half-size.</t>
+          <t>Commodity sleeve CONFIRMED ON first time (V034 GSG 31.75 &gt; 10m-SMA 25.35). Primary commodity promotion post-gate. Size 0.75% (corr+binary haircut + TSLA earnings tonight cross-asset risk + FOMC Apr-28 tail). PARTIAL checklist #6 (C=0, structural edge only) - same precedent as P009 SPY half-size. | FILLED 2026-04-22 21:33:20 UTC+8 @ 95.13 limit/buy (BZUSDT Perp, 1,006.48 USDT, ~10.58 units). Fill $0.63 above upper rec range $94.50. Actual fill captured here; Entry_Price 94.25 preserved as signal-time rec price. | SIZE REDUCED 2026-04-22 22:27 UTC+8 -- sold 147.21 USDT @ 94.97 market reduce-only (BZUSDT Perp). Remaining: 859.27 USDT (~9.03 units). Reason: overexposure correction. Heat 3.09% -&gt; 2.91%.</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY7"/>
+  <dimension ref="A1:BY8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="33" min="1" max="1"/>
@@ -1972,6 +1972,181 @@
       <c r="BY7" t="inlineStr">
         <is>
           <t>2026-04-21/market-brief-2026-04-21.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9237</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69.88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="G8" t="n">
+        <v>285</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.294</v>
+      </c>
+      <c r="S8" t="n">
+        <v>711.21</v>
+      </c>
+      <c r="T8" t="n">
+        <v>655.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>273.17</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>339.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>255.36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>674.72</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>487.48</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>152.62</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>389.1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-35.62</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>97.16</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.035</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2019.8</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1479</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>77536</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2322</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>883</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>493157</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md v1</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="33" min="1" max="1"/>
@@ -10667,6 +10842,84 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>2026-04-21/market-brief-2026-04-21.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RISK-ON / OIL-ELEVATED - HORMUZ BLOCKADE (SHIPPING ATTACKS), CEASEFIRE EXTENDED, INTC EARNINGS TONIGHT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>POSITIVE (records)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ELEVATED-OIL-DRIVEN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CAUTIOUS (5d pre-FOMC)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LOOSE-BUT-TIGHTENING-AT-MARGIN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RISK-ON-FRAGILE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RECOVERY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NEGATIVE (most since 2023; squeeze setup)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S+1 (addr 493K above 400K threshold; sleeve OFF pending May-01 Faber)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>INTC Q1 earnings tonight AC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Brent 100 / WTI 95 re-cross</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Apr-24 Flash PMI stagflation read into FOMC Apr-28-29</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>P013 INTC (pending); P014 AAPL (re-eligible); P009 SPY; P010 EWJ; P016 Brent</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md v1</t>
         </is>
       </c>
     </row>
@@ -15782,7 +16035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.86328125" customWidth="1" style="33" min="1" max="1"/>
@@ -17043,6 +17296,234 @@
       <c r="L30" t="inlineStr">
         <is>
           <t>2026-04-21/market-brief-2026-04-21.md v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B31" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hormuz shipping attacks - Iran seized 2 container ships + attacked 3rd; refused to reopen; US CENTCOM turnaways 31</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Brent, WTI, Gold, Silver, SPY, QQQ, EWJ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Supply shock sticky; ceasefire extension narrowed to oil-shipping-only freeze (Leavitt). Not de-escalation.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B32" s="34" t="n">
+        <v>46136</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Flash PMI US - first post-Hormuz growth+inflation read</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SPY, QQQ, DXY, Bonds</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>March composite 51.4 (11m low). Miss &lt;50 = recession signal hits P009/P010. Above 52 = resilience. Into FOMC amplified.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B33" s="34" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AAPL P014 time-stop pre-May-01 earnings exit</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>P014 must exit before May-01 earnings binary IF entered. Re-eligible Apr-23 ($273.17 back in zone $271-274).</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B34" s="34" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Faber overlay monthly review - sleeve gate flip</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SPY, GSG, BTC, EWJ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BTC must close above $91,523 at Apr-30 to flip crypto sleeve ON ($14K away from $77,536). Equity/commodity gates remain ON.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B35" s="34" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GOOGL Q1 earnings AC (P015 entry trigger; date correction from earlier Apr-22 log)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GOOGL, QQQ, NVDA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>88 pct Mag7 Q1 beat rate. P015 entry Apr-30 AM on beat. C+1 scored pre-earnings.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B36" s="34" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMZN Q1 earnings AC (date correction from Apr-23 log)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AMZN, QQQ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AWS growth, $125B capex leverage; same-day as FOMC + META.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="33" min="1" max="1"/>
@@ -17561,6 +18042,63 @@
       </c>
       <c r="S7" t="n">
         <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DGS2, DFII10, T10YIE (FRED 2d stale beyond 1d window)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HY OAS (T3 2d at limit); WTI/Gold/Silver/Copper basis-mom (T3 6d DEGRADED)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DEGRADED (Brent fresh; WTI/Gold/Silver/Copper T3 &gt;5d)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DEGRADED</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-04-23/market-brief-2026-04-23.md v1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6th consecutive failure for WTI/Gold/Silver/Copper basis-mom retrieval; FRED rates fallback T3 &gt;1d window flags MISSING per protocol. Infrastructure fix HIGH priority on compute_audit_additions.py futures_curves.csv population.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Trade/master-data-log.xlsx
+++ b/Trade/master-data-log.xlsx
@@ -3235,7 +3235,7 @@
       </c>
       <c r="Q9" s="24" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAGGED</t>
         </is>
       </c>
       <c r="R9" s="16" t="n"/>
@@ -3243,7 +3243,7 @@
       <c r="T9" s="16" t="n"/>
       <c r="U9" s="16" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="V9" s="16" t="n"/>
@@ -3251,7 +3251,7 @@
       <c r="X9" s="16" t="n"/>
       <c r="Y9" s="21" t="inlineStr">
         <is>
-          <t>P013. Entry AFTER Apr-23 AC beat confirmation (~$68-72 limit). Sum+4 -- highest conviction. Terafab foundry validation thesis. Entry gate: INTC beat + Terafab milestone. Inv 2026-06-23.</t>
+          <t>P013. Entry AFTER Apr-23 AC beat confirmation (~$68-72 limit). Sum+4 -- highest conviction. Terafab foundry validation thesis. Entry gate: INTC beat + Terafab milestone. Inv 2026-06-23. | FLAGGED 2026-04-24: post-earnings gap to ~$80 blew past $68-72 entry zone. Sum+4 counterfactual retained for system-efficacy measurement — do NOT mark PnL against hypo entry; use exit at FLAGGED_date price for reference.</t>
         </is>
       </c>
     </row>
@@ -3318,23 +3318,27 @@
       </c>
       <c r="Q10" s="24" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="R10" s="16" t="n"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R10" s="16" t="n">
+        <v>274.62</v>
+      </c>
       <c r="S10" s="16" t="n"/>
       <c r="T10" s="16" t="n"/>
       <c r="U10" s="16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="V10" s="16" t="n"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V10" s="16" t="n">
+        <v>274.62</v>
+      </c>
       <c r="W10" s="16" t="n"/>
       <c r="X10" s="16" t="n"/>
       <c r="Y10" s="21" t="inlineStr">
         <is>
-          <t>P014. Limit ~$271-274. Stop ~$264-267 (2x ATR). HARD time-stop 2026-04-30 -- MUST exit before May-1 earnings. C=0; edge is structural momentum only. In zone at $273 (Apr-22).</t>
+          <t>P014. Limit ~$271-274. Stop ~$264-267 (2x ATR). HARD time-stop 2026-04-30 -- MUST exit before May-1 earnings. C=0; edge is structural momentum only. In zone at $273 (Apr-22). | FILLED 2026-04-23 20:45 UTC+8 avg $274.62 (2 tranches). Actual = Hypo (no slippage vs rec mid $272.50; entry at top of zone).</t>
         </is>
       </c>
     </row>
@@ -9229,14 +9233,19 @@
           <t>RISK-ON/GEOPOLITICAL-BINARY-CEASEFIRE-EXPIRED</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Post-rally entry risk</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VOIDED</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -9246,7 +9255,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>NEW PROMOTION. V026 residual +13.89% (A) T=+1. Sum+4 highest conviction signal. Entry AFTER Apr-23 AC beat (Apr-24 morning). Size 1.0% full (V027 z+1.65 capital expansion). ATR ~$2.50.</t>
+          <t>NEW PROMOTION. V026 residual +13.89% (A) T=+1. Sum+4 highest conviction signal. Entry AFTER Apr-23 AC beat (Apr-24 morning). Size 1.0% full (V027 z+1.65 capital expansion). ATR ~$2.50. | VOIDED 2026-04-24: INTC gapped to ~$80 post Q1 earnings beat, far above $68-72 entry zone (+11-17% above zone top, +22% above $65.27 pre-ref, beyond the ±9.87% options-implied move). Classified post-rally entry risk per HypoLedger FLAGGED criteria. No position taken. Chasing would break stop math (2x ATR stop ~$74-76 collides with target $78-82). Alt: controlled pullback to $72-74 zone within 3-5 sessions at 0.5% half-size, stop $68.</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -9331,7 +9340,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -9346,7 +9355,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>NEW PROMOTION. V026 residual +4.68% T=+1. C=0 structural only. Size 0.75% corr haircut vs SPY. Hard time-stop 2026-04-30 BINDING.</t>
+          <t>NEW PROMOTION. V026 residual +4.68% T=+1. C=0 structural only. Size 0.75% corr haircut vs SPY. Hard time-stop 2026-04-30 BINDING. | FILLED 2026-04-23 20:45 UTC+8: T1 398.22 USDT @ 274.63 (limit), T2 447.62 USDT @ 274.61 (limit). Total 845.84 USDT, avg 274.62, ~3.080 units. Stop 266.50. Actual risk 0.63% vs rec 0.75% (slight undersize). Entry at top of $271-274 zone. HARD time-stop 2026-04-30 BINDING.</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
